--- a/education_surveys/024_learning_planning_understanding_survey--education_surveys.xlsx
+++ b/education_surveys/024_learning_planning_understanding_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -988,12 +988,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>learning_goals</t>
+          <t>learning_goals_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Learning Goals</t>
+          <t>Learning Goals 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>learning_planning_understanding</t>
+          <t>learning_planning_understanding_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Learning Planning Understanding</t>
+          <t>Learning Planning Understanding 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>education_programs</t>
+          <t>education_programs_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Education Programs</t>
+          <t>Education Programs 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1109,7 +1109,7 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1627,7 +1627,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>learning_planning_understanding_choices</t>
+          <t>learning_planning_understanding_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1644,7 +1644,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>learning_planning_understanding_choices</t>
+          <t>learning_planning_understanding_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>learning_planning_understanding_choices</t>
+          <t>learning_planning_understanding_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1678,7 +1678,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>learning_planning_understanding_choices</t>
+          <t>learning_planning_understanding_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>learning_planning_understanding_choices</t>
+          <t>learning_planning_understanding_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1712,7 +1712,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>education_programs_choices</t>
+          <t>education_programs_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>education_programs_choices</t>
+          <t>education_programs_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
